--- a/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.2</t>
+    <t>0.8.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T06:42:57+00:00</t>
+    <t>2024-03-15T09:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.3</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T09:00:42+00:00</t>
+    <t>2024-03-17T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>

--- a/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-06T16:49:55+00:00</t>
+    <t>2024-04-28T16:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/StructureDefinition/no-basis-PractitionerRole</t>
+    <t>http://hl7.no/fhir/StructureDefinition/no-basis-PractitionerRole</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-28T16:36:28+00:00</t>
+    <t>2024-06-04T05:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="386">
   <si>
     <t>Property</t>
   </si>
@@ -42,13 +42,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>no-basis-PractitionerRole (shadow)</t>
+    <t>no-basis-PractitionerRole</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T06:11:20+00:00</t>
+    <t>2019-05-20</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Shadow profile of no-basis-PractitionerRole that will be replaced by [no-basis-PractitionerRole](https://simplifier.net/hl7norwayno-basis/nobasispractitionerrole)</t>
+    <t>Basisprofil for Norwegian PractitionerRole information. Defined by The Norwegian Directorate of eHealth and HL7 Norway. Should be used as a basis for further profiling in use-cases where specific role information is available. The basis profile is open, but derived profiles should close down the information elements according to specifications relevant to the use-case.
+The main use-case of no-basis-PractitionerRole is to represent the role or function of a Practitioner wihtin an organization. The resource can include information about services performed by a Practitioner, a location where the practitioner performes the functions as well as information about the nature of the employment at an organization.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -588,7 +589,8 @@
     <t>Roles which this practitioner may perform</t>
   </si>
   <si>
-    <t>Roles which this practitioner is authorized to perform for the organization.</t>
+    <t>no-basis: Codes related to what function the Practitioner may perform
+Roles which this practitioner is authorized to perform for the organization.</t>
   </si>
   <si>
     <t>A person may have more than one role.</t>
@@ -606,19 +608,281 @@
     <t>http://hl7.org/fhir/ValueSet/practitioner-role</t>
   </si>
   <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
   </si>
   <si>
     <t>.code</t>
   </si>
   <si>
+    <t>PractitionerRole.code:functions</t>
+  </si>
+  <si>
+    <t>functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">helsepersonells funksjoner
+</t>
+  </si>
+  <si>
+    <t>no-basis: Codes from urn:oid:2.16.578.1.12.4.1.1.9034 Helsepersonells funksjoner mv. (OID=9034)
+Roles which this practitioner is authorized to perform for the organization.</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.1.9034</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.coding</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.coding.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.coding.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.coding.system</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the Helsepersonellregisterets (HPR) klassifikasjon av spesialiteter (OID=9034)</t>
+  </si>
+  <si>
+    <t>The identification of the code system Helsepersonellregisterets (HPR) klassifikasjon av spesialiteter (OID=9034)</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.coding.version</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.coding.code</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.coding.display</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.coding.userSelected</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code:functions.text</t>
+  </si>
+  <si>
+    <t>PractitionerRole.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
     <t>Specific specialty of the practitioner</t>
   </si>
   <si>
-    <t>Specific specialty of the practitioner.</t>
+    <t>no-basis: code related to a speciality that the Practitioner can perform in the role within an organization
+Specific specialty of the practitioner.</t>
   </si>
   <si>
     <t>Specific specialty associated with the agency.</t>
@@ -634,6 +898,104 @@
   </si>
   <si>
     <t>./Specialty</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline</t>
+  </si>
+  <si>
+    <t>discipline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fagområde
+</t>
+  </si>
+  <si>
+    <t>Specific discipline of practitioner</t>
+  </si>
+  <si>
+    <t>The Discipline the practitioner operates within the organization.</t>
+  </si>
+  <si>
+    <t>Specific discipline</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.1.8451</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.coding</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.coding</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.coding.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.coding.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.coding.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.coding.extension</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.coding.system</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.coding.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fagområde
+</t>
+  </si>
+  <si>
+    <t>The identification of the code system</t>
+  </si>
+  <si>
+    <t>The identification of the code system Fagområde (OID=8451)</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.coding.version</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.coding.version</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.coding.code</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.coding.code</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.coding.display</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.coding.display</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.coding.userSelected</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.coding.userSelected</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty:discipline.text</t>
+  </si>
+  <si>
+    <t>PractitionerRole.specialty.text</t>
   </si>
   <si>
     <t>PractitionerRole.location</t>
@@ -718,29 +1080,7 @@
     <t>PractitionerRole.availableTime.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>PractitionerRole.availableTime.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>PractitionerRole.availableTime.modifierExtension</t>
@@ -867,7 +1207,8 @@
     <t>Technical endpoints providing access to services operated for the practitioner with this role</t>
   </si>
   <si>
-    <t>Technical endpoints providing access to services operated for the practitioner with this role.</t>
+    <t>no-basis: don't use this element to reference endpoints registered in the Norwegian Address register (endpoints connected to a kommunikasjonspart in tjenestebasert adressering). Endpoints registered in the Norwegian Address register should only be referenced through a kommunikasjonspart-Organization resource.
+Technical endpoints providing access to services operated for the practitioner with this role.</t>
   </si>
   <si>
     <t>Organizations have multiple systems that provide various services and ,ay also be different for practitioners too.@@ -1166,10 +1507,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN36"/>
+  <dimension ref="A1:AN60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.96875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.94921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.96875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1197,7 +1538,7 @@
     <col min="26" max="26" width="43.75" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="46.96875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3003,16 +3344,14 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>181</v>
@@ -3030,10 +3369,10 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>169</v>
@@ -3044,14 +3383,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="D17" t="s" s="2">
-        <v>75</v>
+        <v>196</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3073,13 +3414,17 @@
         <v>182</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>75</v>
       </c>
@@ -3105,11 +3450,9 @@
       <c r="X17" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>75</v>
@@ -3127,7 +3470,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3142,13 +3485,13 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>75</v>
@@ -3156,7 +3499,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>200</v>
@@ -3170,7 +3513,7 @@
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -3179,7 +3522,7 @@
         <v>75</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>201</v>
@@ -3239,43 +3582,43 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>205</v>
+        <v>75</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3294,15 +3637,17 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N19" s="2"/>
+      <c r="N19" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3339,19 +3684,19 @@
         <v>75</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3363,13 +3708,13 @@
         <v>75</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>75</v>
@@ -3380,7 +3725,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>213</v>
@@ -3414,9 +3759,11 @@
       <c r="M20" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3465,7 +3812,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3480,10 +3827,10 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>75</v>
@@ -3494,10 +3841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3508,7 +3855,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -3520,17 +3867,15 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -3579,25 +3924,25 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>75</v>
@@ -3608,21 +3953,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>75</v>
@@ -3634,15 +3979,17 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>75</v>
@@ -3679,37 +4026,37 @@
         <v>75</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>75</v>
@@ -3720,21 +4067,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>75</v>
@@ -3743,27 +4090,29 @@
         <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>75</v>
@@ -3805,25 +4154,25 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AL23" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>75</v>
@@ -3834,46 +4183,44 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>75</v>
       </c>
@@ -3921,25 +4268,25 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>129</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>75</v>
@@ -3950,10 +4297,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3961,10 +4308,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>75</v>
@@ -3973,19 +4320,21 @@
         <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4009,13 +4358,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>242</v>
+        <v>75</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>243</v>
+        <v>75</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>244</v>
+        <v>75</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4033,13 +4382,13 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>75</v>
@@ -4048,10 +4397,10 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>75</v>
+        <v>249</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>75</v>
@@ -4062,10 +4411,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4085,19 +4434,21 @@
         <v>75</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>153</v>
+        <v>201</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4145,7 +4496,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4160,10 +4511,10 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>75</v>
@@ -4174,10 +4525,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4197,21 +4548,23 @@
         <v>75</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>249</v>
+        <v>153</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -4259,7 +4612,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4274,10 +4627,10 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>75</v>
@@ -4288,10 +4641,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4311,21 +4664,23 @@
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4373,7 +4728,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4388,10 +4743,10 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>75</v>
+        <v>275</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>75</v>
@@ -4402,10 +4757,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4425,16 +4780,16 @@
         <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4461,31 +4816,29 @@
         <v>75</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>75</v>
+        <v>281</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4500,13 +4853,13 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>75</v>
+        <v>282</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>75</v>
+        <v>284</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>75</v>
@@ -4514,21 +4867,23 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>75</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>75</v>
@@ -4537,16 +4892,16 @@
         <v>75</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>228</v>
+        <v>289</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4573,13 +4928,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>75</v>
+        <v>290</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -4597,28 +4952,28 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>75</v>
+        <v>282</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>230</v>
+        <v>283</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>75</v>
+        <v>284</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>75</v>
@@ -4626,21 +4981,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>75</v>
@@ -4652,17 +5007,15 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -4711,25 +5064,25 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>75</v>
@@ -4740,14 +5093,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4760,26 +5113,24 @@
         <v>75</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="O32" t="s" s="2">
-        <v>141</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>75</v>
       </c>
@@ -4815,19 +5166,19 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4845,7 +5196,7 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>129</v>
+        <v>205</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>75</v>
@@ -4856,10 +5207,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4867,10 +5218,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
@@ -4879,19 +5230,23 @@
         <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
@@ -4939,13 +5294,13 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>75</v>
@@ -4954,10 +5309,10 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>75</v>
@@ -4968,10 +5323,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4994,13 +5349,13 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>202</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5051,7 +5406,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5063,13 +5418,13 @@
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>75</v>
@@ -5080,21 +5435,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>75</v>
@@ -5106,15 +5461,17 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>269</v>
+        <v>133</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5151,37 +5508,37 @@
         <v>75</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>75</v>
@@ -5192,21 +5549,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>75</v>
+        <v>304</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -5215,27 +5572,29 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>272</v>
+        <v>100</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>75</v>
@@ -5277,13 +5636,13 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>75</v>
@@ -5292,15 +5651,2739 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>75</v>
+        <v>233</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>75</v>
       </c>
     </row>

--- a/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-PractitionerRole.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>
